--- a/data/trans_camb/P16A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 10,95</t>
+          <t>0,38; 10,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,69</t>
+          <t>-1,15; 8,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 6,21</t>
+          <t>-3,5; 5,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 9,15</t>
+          <t>-1,11; 9,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,3</t>
+          <t>-3,16; 6,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,35</t>
+          <t>-4,46; 3,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,29</t>
+          <t>1,1; 8,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,37</t>
+          <t>-0,58; 5,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,5</t>
+          <t>-3,2; 3,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 212,11</t>
+          <t>0,96; 215,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 173,26</t>
+          <t>-13,53; 177,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 121,4</t>
+          <t>-37,89; 115,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 181,2</t>
+          <t>-16,2; 183,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 135,3</t>
+          <t>-34,34; 127,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 67,34</t>
+          <t>-46,19; 79,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 150,42</t>
+          <t>9,86; 149,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 109,44</t>
+          <t>-10,11; 99,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 60,88</t>
+          <t>-35,32; 65,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,38</t>
+          <t>2,53; 10,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 4,0</t>
+          <t>-2,3; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,35</t>
+          <t>-5,86; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,41</t>
+          <t>-0,97; 5,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,75</t>
+          <t>-1,82; 4,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,29</t>
+          <t>-2,49; 3,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,72</t>
+          <t>1,47; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,31</t>
+          <t>-1,22; 3,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,17</t>
+          <t>-3,41; 1,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,13; 213,44</t>
+          <t>29,64; 212,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 83,85</t>
+          <t>-30,96; 89,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 13,28</t>
+          <t>-73,24; 8,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 118,44</t>
+          <t>-13,95; 121,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 99,23</t>
+          <t>-25,13; 100,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 67,8</t>
+          <t>-32,9; 75,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 126,65</t>
+          <t>18,21; 130,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 66,36</t>
+          <t>-17,24; 69,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 22,89</t>
+          <t>-45,52; 21,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,03</t>
+          <t>2,7; 10,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,56</t>
+          <t>-2,32; 4,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,01</t>
+          <t>-1,38; 5,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,65</t>
+          <t>4,7; 12,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,34</t>
+          <t>2,5; 9,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,48</t>
+          <t>4,32; 10,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,39</t>
+          <t>4,82; 10,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,99</t>
+          <t>1,32; 6,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,27</t>
+          <t>2,59; 7,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,68; 429,69</t>
+          <t>37,09; 360,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 149,66</t>
+          <t>-38,79; 190,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 232,88</t>
+          <t>-22,59; 192,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141,21; 1084,96</t>
+          <t>125,93; 1316,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,13; 819,6</t>
+          <t>55,08; 958,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>122,22; 1121,85</t>
+          <t>109,93; 1092,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106,43; 452,5</t>
+          <t>106,58; 436,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,57; 248,52</t>
+          <t>26,62; 268,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,14; 320,13</t>
+          <t>54,78; 315,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,99</t>
+          <t>-2,99; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 6,9</t>
+          <t>-0,64; 6,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 7,7</t>
+          <t>-1,59; 7,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,28</t>
+          <t>0,8; 8,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,98</t>
+          <t>-1,96; 4,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,76</t>
+          <t>-3,02; 4,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,94</t>
+          <t>-0,07; 4,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,88</t>
+          <t>-0,03; 4,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,31</t>
+          <t>-1,63; 4,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 103,94</t>
+          <t>-38,67; 109,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 169,41</t>
+          <t>-11,16; 164,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 191,63</t>
+          <t>-22,73; 194,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,3; 205,79</t>
+          <t>7,55; 214,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 127,01</t>
+          <t>-29,94; 131,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 100,34</t>
+          <t>-40,68; 109,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 111,13</t>
+          <t>-1,05; 109,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 108,85</t>
+          <t>-1,59; 109,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 93,81</t>
+          <t>-24,62; 92,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,51</t>
+          <t>-0,58; 10,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,2</t>
+          <t>-5,76; 4,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 4,56</t>
+          <t>-4,82; 4,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 8,05</t>
+          <t>-2,74; 8,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 5,58</t>
+          <t>-4,16; 5,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 8,43</t>
+          <t>-0,88; 8,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 8,11</t>
+          <t>0,17; 7,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,73</t>
+          <t>-3,41; 3,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,68</t>
+          <t>-1,54; 5,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 225,11</t>
+          <t>-10,29; 205,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 101,02</t>
+          <t>-59,76; 86,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 98,86</t>
+          <t>-50,44; 86,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 167,6</t>
+          <t>-30,69; 175,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 119,34</t>
+          <t>-44,41; 124,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 195,45</t>
+          <t>-10,66; 194,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 148,82</t>
+          <t>0,57; 147,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 70,56</t>
+          <t>-38,84; 70,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 104,5</t>
+          <t>-18,46; 103,64</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,05; 14,23</t>
+          <t>4,13; 14,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,24</t>
+          <t>-3,44; 5,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,25</t>
+          <t>-1,8; 6,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,86</t>
+          <t>0,25; 9,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 8,18</t>
+          <t>-0,83; 8,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,41</t>
+          <t>-2,83; 5,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,22</t>
+          <t>3,34; 10,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,07</t>
+          <t>-1,01; 5,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,77</t>
+          <t>-1,05; 4,68</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44,99; 350,7</t>
+          <t>36,78; 331,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 151,8</t>
+          <t>-43,98; 139,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 144,57</t>
+          <t>-24,84; 161,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 243,41</t>
+          <t>-2,36; 259,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 211,71</t>
+          <t>-17,48; 229,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 158,78</t>
+          <t>-37,06; 142,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46,08; 236,65</t>
+          <t>43,53; 220,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 110,78</t>
+          <t>-14,65; 112,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 106,2</t>
+          <t>-15,15; 103,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,1</t>
+          <t>-2,53; 3,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,64</t>
+          <t>-2,7; 3,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,88</t>
+          <t>-0,51; 7,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,58</t>
+          <t>-2,74; 2,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,32</t>
+          <t>-1,43; 4,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,48</t>
+          <t>-3,47; 4,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,36</t>
+          <t>-1,57; 2,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,1</t>
+          <t>-1,2; 3,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,45</t>
+          <t>-1,74; 4,39</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 62,76</t>
+          <t>-26,55; 60,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 56,46</t>
+          <t>-29,44; 62,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 108,0</t>
+          <t>-7,03; 114,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 55,61</t>
+          <t>-35,86; 51,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 88,17</t>
+          <t>-19,97; 88,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 82,42</t>
+          <t>-45,84; 84,75</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 39,38</t>
+          <t>-19,74; 42,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 52,81</t>
+          <t>-15,11; 50,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 70,62</t>
+          <t>-20,32; 69,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,59</t>
+          <t>-5,83; -0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,41</t>
+          <t>-4,02; 1,34</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -1,78</t>
+          <t>-8,34; -1,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,19</t>
+          <t>-5,27; -0,14</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,1</t>
+          <t>-2,15; 3,97</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,27</t>
+          <t>-5,5; -0,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -0,95</t>
+          <t>-4,78; -0,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,14</t>
+          <t>-2,14; 1,92</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -1,91</t>
+          <t>-6,34; -2,0</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,77; -8,22</t>
+          <t>-59,91; -5,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 20,73</t>
+          <t>-42,48; 19,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-80,19; -25,12</t>
+          <t>-81,5; -24,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-51,04; -2,28</t>
+          <t>-50,98; -1,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 54,12</t>
+          <t>-21,14; 51,75</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,58; -1,85</t>
+          <t>-51,97; -7,31</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-49,34; -8,95</t>
+          <t>-49,67; -13,03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 30,55</t>
+          <t>-22,81; 26,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-68,19; -25,39</t>
+          <t>-67,59; -26,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,97</t>
+          <t>1,16; 3,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,11</t>
+          <t>-1,98; 1,09</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,29</t>
+          <t>0,64; 3,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,18</t>
+          <t>0,65; 3,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,04</t>
+          <t>-0,72; 1,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,08</t>
+          <t>1,28; 3,1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,22</t>
+          <t>0,4; 2,35</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,33</t>
+          <t>-0,75; 1,31</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,76; 61,9</t>
+          <t>15,9; 61,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 36,0</t>
+          <t>-7,9; 32,24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 17,16</t>
+          <t>-27,16; 16,71</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9,78; 56,37</t>
+          <t>8,64; 53,27</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,59; 54,88</t>
+          <t>9,37; 58,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 34,57</t>
+          <t>-10,29; 31,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,82; 48,01</t>
+          <t>17,66; 50,05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,53; 35,43</t>
+          <t>5,51; 37,07</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 21,44</t>
+          <t>-10,58; 20,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 10,75</t>
+          <t>0,15; 10,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,82</t>
+          <t>-1,04; 8,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,77</t>
+          <t>-4,14; 4,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 9,36</t>
+          <t>-1,29; 9,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 6,24</t>
+          <t>-2,93; 5,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 3,53</t>
+          <t>-5,08; 3,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,42</t>
+          <t>1,14; 8,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,84</t>
+          <t>-0,58; 6,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,59</t>
+          <t>-3,25; 2,65</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-6,46%</t>
+          <t>-10,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>-2,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 215,5</t>
+          <t>-1,16; 217,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 177,32</t>
+          <t>-12,67; 180,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 115,33</t>
+          <t>-45,15; 93,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 183,98</t>
+          <t>-12,53; 183,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 127,85</t>
+          <t>-32,67; 125,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 79,02</t>
+          <t>-49,74; 62,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 149,76</t>
+          <t>12,18; 154,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 99,39</t>
+          <t>-8,7; 104,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 65,23</t>
+          <t>-36,12; 49,09</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,7</t>
+          <t>2,97; 10,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,07</t>
+          <t>-2,39; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,25</t>
+          <t>-5,98; 0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,69</t>
+          <t>-1,06; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,85</t>
+          <t>-1,7; 4,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,61</t>
+          <t>-2,51; 3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,9</t>
+          <t>2,0; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,53</t>
+          <t>-1,03; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,19</t>
+          <t>-3,47; 0,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-43,11%</t>
+          <t>-44,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,12%</t>
+          <t>-20,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 212,11</t>
+          <t>35,37; 238,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 89,29</t>
+          <t>-31,01; 98,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,24; 8,41</t>
+          <t>-72,16; 7,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 121,43</t>
+          <t>-14,68; 110,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 100,7</t>
+          <t>-25,48; 96,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,9; 75,38</t>
+          <t>-32,96; 67,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 130,07</t>
+          <t>25,03; 129,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 69,12</t>
+          <t>-14,75; 64,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,52; 21,66</t>
+          <t>-47,06; 15,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>5,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 10,72</t>
+          <t>2,33; 11,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,99</t>
+          <t>-1,93; 4,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,68</t>
+          <t>-0,03; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,4</t>
+          <t>5,4; 12,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,74</t>
+          <t>2,4; 9,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,34</t>
+          <t>4,85; 10,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,34</t>
+          <t>5,13; 10,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,16</t>
+          <t>1,06; 6,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,15</t>
+          <t>3,34; 8,07</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>364,06%</t>
+          <t>386,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>154,08%</t>
+          <t>175,01%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,09; 360,44</t>
+          <t>32,56; 409,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 190,69</t>
+          <t>-32,45; 199,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 192,23</t>
+          <t>-8,5; 268,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125,93; 1316,55</t>
+          <t>153,59; 1286,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,08; 958,11</t>
+          <t>67,03; 860,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109,93; 1092,09</t>
+          <t>106,55; 994,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106,58; 436,23</t>
+          <t>116,88; 512,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,62; 268,48</t>
+          <t>22,28; 270,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54,78; 315,06</t>
+          <t>76,68; 386,92</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,44</t>
+          <t>-2,89; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,79</t>
+          <t>-0,58; 6,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 7,96</t>
+          <t>-1,64; 7,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,45</t>
+          <t>0,4; 8,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,98</t>
+          <t>-2,06; 4,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,04</t>
+          <t>-1,54; 5,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,79</t>
+          <t>-0,22; 5,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,8</t>
+          <t>-0,36; 4,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,38</t>
+          <t>-0,87; 4,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 109,67</t>
+          <t>-42,3; 95,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 164,83</t>
+          <t>-10,58; 166,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 194,47</t>
+          <t>-25,13; 180,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 214,64</t>
+          <t>2,5; 202,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 131,44</t>
+          <t>-32,87; 125,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 109,01</t>
+          <t>-25,69; 135,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 109,61</t>
+          <t>-4,1; 120,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 109,71</t>
+          <t>-6,72; 108,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 92,94</t>
+          <t>-15,19; 102,66</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 10,65</t>
+          <t>-0,35; 11,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 4,26</t>
+          <t>-5,1; 4,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,08</t>
+          <t>-4,54; 4,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 8,3</t>
+          <t>-2,63; 8,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,64</t>
+          <t>-4,53; 5,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,92</t>
+          <t>-0,9; 8,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,89</t>
+          <t>-0,26; 7,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,76</t>
+          <t>-3,23; 3,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,39</t>
+          <t>-1,24; 5,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,77%</t>
+          <t>-2,56%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 205,17</t>
+          <t>-7,34; 244,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 86,56</t>
+          <t>-54,29; 106,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 86,57</t>
+          <t>-47,79; 110,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 175,09</t>
+          <t>-29,63; 183,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 124,18</t>
+          <t>-45,92; 118,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 194,61</t>
+          <t>-11,04; 203,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,57; 147,1</t>
+          <t>-4,26; 140,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 70,67</t>
+          <t>-36,76; 74,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 103,64</t>
+          <t>-14,99; 109,5</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,13; 14,43</t>
+          <t>4,14; 14,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,45</t>
+          <t>-3,56; 5,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,16</t>
+          <t>-2,1; 5,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,25; 9,28</t>
+          <t>-0,2; 8,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,18</t>
+          <t>-0,59; 7,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,31</t>
+          <t>-2,13; 5,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,56</t>
+          <t>3,41; 10,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,15</t>
+          <t>-0,62; 5,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,68</t>
+          <t>-0,87; 4,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36,78; 331,33</t>
+          <t>43,71; 315,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 139,55</t>
+          <t>-43,55; 112,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 161,49</t>
+          <t>-29,66; 137,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 259,36</t>
+          <t>-5,49; 239,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 229,72</t>
+          <t>-12,37; 212,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 142,29</t>
+          <t>-28,23; 141,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43,53; 220,89</t>
+          <t>44,14; 234,47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 112,12</t>
+          <t>-10,93; 128,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 103,29</t>
+          <t>-14,12; 107,07</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,93</t>
+          <t>-2,69; 3,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,57</t>
+          <t>-2,8; 3,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,17</t>
+          <t>-0,89; 6,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,56</t>
+          <t>-2,94; 2,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,32</t>
+          <t>-1,32; 4,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,47</t>
+          <t>0,59; 6,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,53</t>
+          <t>-1,84; 2,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,01</t>
+          <t>-1,11; 3,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,39</t>
+          <t>0,88; 5,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 60,91</t>
+          <t>-28,13; 56,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 62,17</t>
+          <t>-29,32; 59,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 114,69</t>
+          <t>-10,75; 102,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 51,18</t>
+          <t>-38,42; 53,03</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 88,28</t>
+          <t>-17,54; 96,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 84,75</t>
+          <t>7,55; 137,12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 42,36</t>
+          <t>-22,9; 38,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 50,17</t>
+          <t>-13,8; 52,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 69,83</t>
+          <t>10,01; 91,55</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>-3,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,5</t>
+          <t>-5,76; -0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,34</t>
+          <t>-4,16; 1,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -1,78</t>
+          <t>-5,6; -0,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,14</t>
+          <t>-5,18; -0,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,97</t>
+          <t>-2,12; 4,06</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -0,58</t>
+          <t>-5,63; -0,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,96</t>
+          <t>-5,15; -1,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,92</t>
+          <t>-2,19; 2,02</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -2,0</t>
+          <t>-4,8; -1,29</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-53,39%</t>
+          <t>-34,55%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-33,44%</t>
+          <t>-35,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-44,67%</t>
+          <t>-35,09%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-59,91; -5,84</t>
+          <t>-60,4; -6,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 19,3</t>
+          <t>-41,81; 18,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-81,5; -24,91</t>
+          <t>-56,87; -4,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-50,98; -1,45</t>
+          <t>-49,85; 0,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 51,75</t>
+          <t>-19,96; 53,77</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-51,97; -7,31</t>
+          <t>-53,37; -6,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-49,67; -13,03</t>
+          <t>-51,61; -15,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 26,29</t>
+          <t>-22,91; 27,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-67,59; -26,85</t>
+          <t>-49,72; -16,14</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,85</t>
+          <t>1,09; 3,9</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,09</t>
+          <t>-1,04; 1,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,18</t>
+          <t>0,5; 3,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,62; 3,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,91</t>
+          <t>0,07; 2,47</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,1</t>
+          <t>1,27; 3,09</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,35</t>
+          <t>0,48; 2,24</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,31</t>
+          <t>-0,06; 1,67</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-4,5%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,9; 61,55</t>
+          <t>14,49; 62,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 32,24</t>
+          <t>-7,15; 33,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 16,71</t>
+          <t>-14,12; 26,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,64; 53,27</t>
+          <t>7,16; 54,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,37; 58,99</t>
+          <t>8,7; 56,66</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 31,79</t>
+          <t>1,3; 44,14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,66; 50,05</t>
+          <t>17,75; 49,18</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>5,51; 37,07</t>
+          <t>6,72; 35,94</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 20,97</t>
+          <t>-0,77; 26,99</t>
         </is>
       </c>
     </row>
